--- a/data/trans_dic/IP19C05-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP19C05-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que en su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis</t>
+          <t>Menores que en su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis (tasa de respuesta: 99,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,54</t>
+          <t>0,0; 6,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,39; 12,36</t>
+          <t>1,42; 13,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,47</t>
+          <t>0,0; 8,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,52</t>
+          <t>0,0; 11,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,64</t>
+          <t>0,0; 3,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,04; 8,36</t>
+          <t>0,84; 7,55</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,36</t>
+          <t>0,0; 5,92</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 3,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,47</t>
+          <t>0,0; 9,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,41</t>
+          <t>0,0; 10,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 3,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,24</t>
+          <t>0,0; 7,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,81</t>
+          <t>0,0; 7,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 5,18</t>
+          <t>0,44; 5,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 7,08</t>
+          <t>0,98; 6,8</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,31</t>
+          <t>0,0; 10,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,02</t>
+          <t>0,0; 11,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,9</t>
+          <t>0,0; 7,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,41</t>
+          <t>0,0; 10,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,62</t>
+          <t>0,0; 5,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 8,19</t>
+          <t>0,87; 8,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,52</t>
+          <t>0,0; 5,66</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,67</t>
+          <t>0,0; 3,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 5,96</t>
+          <t>0,66; 6,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,21; 7,6</t>
+          <t>1,12; 7,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,13</t>
+          <t>0,0; 5,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,01</t>
+          <t>0,0; 4,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,02</t>
+          <t>0,0; 5,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,0</t>
+          <t>0,31; 2,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,51</t>
+          <t>0,41; 3,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,64</t>
+          <t>0,99; 4,74</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,98</t>
+          <t>0,0; 7,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,38</t>
+          <t>0,0; 6,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,95; 9,18</t>
+          <t>0,95; 8,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 8,16</t>
+          <t>0,87; 8,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,87</t>
+          <t>0,0; 6,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,49</t>
+          <t>0,0; 3,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,02; 5,45</t>
+          <t>0,89; 5,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 5,8</t>
+          <t>0,9; 5,77</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,0</t>
+          <t>0,0; 8,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,29</t>
+          <t>0,0; 5,13</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,11</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,76</t>
+          <t>0,18; 1,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,39; 4,49</t>
+          <t>1,43; 4,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,34; 4,35</t>
+          <t>1,36; 4,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,15</t>
+          <t>0,2; 2,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,29</t>
+          <t>0,82; 3,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,06</t>
+          <t>0,67; 3,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,42</t>
+          <t>0,33; 1,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,25</t>
+          <t>1,38; 3,36</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,27; 3,0</t>
+          <t>1,28; 3,08</t>
         </is>
       </c>
     </row>
@@ -1404,4 +1405,1283 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis (tasa de respuesta: 99,43%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2371</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1563</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>3029</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1563</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3694</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>683; 6619</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3270</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5831</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3163</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>747; 6730</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5537</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1202</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1789</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>806</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1367</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>3156</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4737</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5956</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3996</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4242</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>442; 5413</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1081; 7462</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1433</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>729</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1388</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2821</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>729</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4310</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3624</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3871</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4301</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4480</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>708; 6827</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3700</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3441</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1551</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>779</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1609</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2149</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2783</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>5050</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3209</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>603; 5802</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1245; 7814</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5730</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4731</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5758</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>603; 5672</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>769; 6787</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>2122; 10190</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>873</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1620</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2581</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2588</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>850</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>873</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>4207</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>3431</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3981</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5515</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>659; 6191</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>638; 5925</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4626</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4953</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>1390; 8820</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1281; 8231</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3003</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3886</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>8630</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>8540</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2837</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>6218</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>5388</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>4940</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>14848</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>13929</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>597; 5637</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>4829; 15340</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>4658; 15317</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>685; 7017</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2822; 11781</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>2341; 10766</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>2180; 10374</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>9379; 22811</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>8847; 21302</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP19C05-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP19C05-Clase-trans_dic.xlsx
@@ -678,12 +678,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,74</t>
+          <t>0,0; 5,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 13,72</t>
+          <t>1,41; 13,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -698,27 +698,27 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,0</t>
+          <t>0,0; 8,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,54</t>
+          <t>0,0; 10,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,04</t>
+          <t>0,0; 3,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 7,55</t>
+          <t>0,84; 8,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,92</t>
+          <t>0,0; 5,26</t>
         </is>
       </c>
     </row>
@@ -793,12 +793,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,97</t>
+          <t>0,0; 8,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,69</t>
+          <t>0,0; 11,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -808,12 +808,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,53</t>
+          <t>0,0; 8,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,85</t>
+          <t>0,0; 7,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -823,12 +823,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 5,38</t>
+          <t>0,44; 5,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 6,8</t>
+          <t>0,68; 7,38</t>
         </is>
       </c>
     </row>
@@ -903,22 +903,22 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 12,15</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>0,0; 10,33</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 11,64</t>
-        </is>
-      </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,25</t>
+          <t>0,0; 6,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,81</t>
+          <t>0,0; 12,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,17 +928,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,07</t>
+          <t>0,0; 3,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 8,37</t>
+          <t>0,89; 7,82</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,66</t>
+          <t>0,0; 5,58</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,27</t>
+          <t>0,0; 3,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,66; 6,36</t>
+          <t>0,0; 6,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,12; 7,03</t>
+          <t>1,12; 6,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,96</t>
+          <t>0,0; 5,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,83</t>
+          <t>0,0; 4,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,54</t>
+          <t>0,0; 5,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,92</t>
+          <t>0,31; 3,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,59</t>
+          <t>0,4; 3,58</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,74</t>
+          <t>0,93; 4,53</t>
         </is>
       </c>
     </row>
@@ -1118,17 +1118,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,28</t>
+          <t>0,0; 8,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,71</t>
+          <t>0,0; 7,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,95; 8,95</t>
+          <t>0,95; 10,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1138,27 +1138,27 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 8,04</t>
+          <t>0,9; 8,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,29</t>
+          <t>0,0; 5,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,97</t>
+          <t>0,0; 3,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 5,66</t>
+          <t>1,23; 5,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,77</t>
+          <t>0,6; 5,14</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,41</t>
+          <t>0,0; 8,28</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,13</t>
+          <t>0,0; 5,1</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,74</t>
+          <t>0,19; 1,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,56</t>
+          <t>1,33; 4,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,36; 4,47</t>
+          <t>1,39; 4,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,05</t>
+          <t>0,2; 1,98</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,44</t>
+          <t>0,82; 3,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,09</t>
+          <t>0,63; 2,95</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,56</t>
+          <t>0,32; 1,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,38; 3,36</t>
+          <t>1,35; 3,29</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,08</t>
+          <t>1,22; 3,19</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3694</t>
+          <t>0; 3119</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>683; 6619</t>
+          <t>680; 6712</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1659,27 +1659,27 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3270</t>
+          <t>0; 3598</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5831</t>
+          <t>0; 5247</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3163</t>
+          <t>0; 3760</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>747; 6730</t>
+          <t>750; 7256</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 5537</t>
+          <t>0; 4917</t>
         </is>
       </c>
     </row>
@@ -1807,12 +1807,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4737</t>
+          <t>0; 4121</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5956</t>
+          <t>0; 6201</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3996</t>
+          <t>0; 4421</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4242</t>
+          <t>0; 4313</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>442; 5413</t>
+          <t>441; 5849</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1081; 7462</t>
+          <t>751; 8096</t>
         </is>
       </c>
     </row>
@@ -1970,22 +1970,22 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4310</t>
+          <t>0; 5070</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3624</t>
+          <t>0; 3215</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3871</t>
+          <t>0; 3628</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4301</t>
+          <t>0; 5004</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1995,17 +1995,17 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4480</t>
+          <t>0; 3216</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>708; 6827</t>
+          <t>721; 6371</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3700</t>
+          <t>0; 3648</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3209</t>
+          <t>0; 2977</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>603; 5802</t>
+          <t>0; 5734</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1245; 7814</t>
+          <t>1245; 7637</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 5730</t>
+          <t>0; 5305</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4731</t>
+          <t>0; 3929</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5758</t>
+          <t>0; 5441</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>603; 5672</t>
+          <t>596; 6598</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>769; 6787</t>
+          <t>762; 6771</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2122; 10190</t>
+          <t>1996; 9745</t>
         </is>
       </c>
     </row>
@@ -2291,17 +2291,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3981</t>
+          <t>0; 4884</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 5515</t>
+          <t>0; 5757</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>659; 6191</t>
+          <t>659; 7091</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2311,27 +2311,27 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>638; 5925</t>
+          <t>663; 6027</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 4626</t>
+          <t>0; 4266</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4953</t>
+          <t>0; 3916</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1390; 8820</t>
+          <t>1923; 9095</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1281; 8231</t>
+          <t>858; 7333</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 3003</t>
+          <t>0; 2958</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 3886</t>
+          <t>0; 3865</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>597; 5637</t>
+          <t>599; 6316</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4829; 15340</t>
+          <t>4492; 14748</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4658; 15317</t>
+          <t>4770; 14824</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>685; 7017</t>
+          <t>683; 6765</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2822; 11781</t>
+          <t>2827; 11033</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2341; 10766</t>
+          <t>2208; 10268</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2180; 10374</t>
+          <t>2101; 10089</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>9379; 22811</t>
+          <t>9206; 22381</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>8847; 21302</t>
+          <t>8463; 22061</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP19C05-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP19C05-Clase-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3,09%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>1,15%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>4,92%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 13,92</t>
+          <t>0,0; 7,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 9,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 6,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,8</t>
+          <t>1,39; 12,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,61</t>
+          <t>0,0; 3,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 8,14</t>
+          <t>1,04; 8,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,26</t>
+          <t>0,0; 5,36</t>
         </is>
       </c>
     </row>
@@ -740,27 +740,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>2,53%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>3,21%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -793,12 +793,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,68</t>
+          <t>0,0; 7,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,13</t>
+          <t>0,0; 8,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -808,12 +808,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,33</t>
+          <t>0,0; 8,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,98</t>
+          <t>0,0; 11,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -823,12 +823,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 5,82</t>
+          <t>0,44; 5,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 7,38</t>
+          <t>0,97; 7,08</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3,49%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>3,43%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2,34%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 6,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,15</t>
+          <t>0,0; 11,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,33</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,8</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,57</t>
+          <t>0,0; 10,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 13,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,64</t>
+          <t>0,0; 3,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 7,82</t>
+          <t>0,88; 8,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,58</t>
+          <t>0,0; 5,52</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>0,61%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>2,2%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>3,1%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,03</t>
+          <t>0,0; 5,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,29</t>
+          <t>0,0; 4,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,12; 6,87</t>
+          <t>0,0; 5,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,52</t>
+          <t>0,0; 2,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,01</t>
+          <t>0,67; 5,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,24</t>
+          <t>1,21; 7,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,4</t>
+          <t>0,31; 3,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,58</t>
+          <t>0,33; 3,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,53</t>
+          <t>0,93; 4,64</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3,51%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>1,6%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>1,97%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>3,73%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,51%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,94</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,0</t>
+          <t>0,87; 8,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,95; 10,25</t>
+          <t>0,0; 6,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 7,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 8,18</t>
+          <t>0,0; 7,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,8</t>
+          <t>0,95; 9,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,14</t>
+          <t>0,0; 3,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,23; 5,83</t>
+          <t>1,02; 5,45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,14</t>
+          <t>0,91; 5,8</t>
         </is>
       </c>
     </row>
@@ -1175,22 +1175,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 11,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,1</t>
+          <t>0,0; 4,29</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,65%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2,56%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>2,49%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,95</t>
+          <t>0,2; 2,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,33; 4,38</t>
+          <t>0,84; 3,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,39; 4,33</t>
+          <t>0,7; 3,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,98</t>
+          <t>0,18; 1,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,22</t>
+          <t>1,39; 4,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,95</t>
+          <t>1,34; 4,35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,52</t>
+          <t>0,29; 1,42</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,29</t>
+          <t>1,4; 3,25</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,19</t>
+          <t>1,27; 3,0</t>
         </is>
       </c>
     </row>
@@ -1438,14 +1438,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1533,32 +1533,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1586,32 +1586,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1563</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>632</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>2371</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>657</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1563</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3119</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>680; 6712</t>
+          <t>0; 3053</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4807</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3582</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3598</t>
+          <t>669; 5960</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5247</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3760</t>
+          <t>0; 3795</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>750; 7256</t>
+          <t>924; 7448</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4917</t>
+          <t>0; 5013</t>
         </is>
       </c>
     </row>
@@ -1701,22 +1701,22 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1754,27 +1754,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>806</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1367</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1202</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1789</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>806</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1367</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4121</t>
+          <t>0; 3844</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 6201</t>
+          <t>0; 4759</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4421</t>
+          <t>0; 4023</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4313</t>
+          <t>0; 6361</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>441; 5849</t>
+          <t>442; 5206</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>751; 8096</t>
+          <t>1070; 7767</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1869,22 +1869,22 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1912,32 +1912,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>642</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>1388</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>1433</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>729</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1388</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3683</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5070</t>
+          <t>0; 4540</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3215</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3628</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5004</t>
+          <t>0; 4303</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4054</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3216</t>
+          <t>0; 3196</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>721; 6371</t>
+          <t>718; 6672</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3648</t>
+          <t>0; 3614</t>
         </is>
       </c>
     </row>
@@ -2022,32 +2022,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2075,32 +2075,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1551</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>779</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1609</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>598</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>2003</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>3441</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1551</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>779</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1609</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2977</t>
+          <t>0; 4936</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5734</t>
+          <t>0; 3924</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1245; 7637</t>
+          <t>0; 5212</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 5305</t>
+          <t>0; 2624</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3929</t>
+          <t>608; 5438</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5441</t>
+          <t>1339; 8445</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>596; 6598</t>
+          <t>598; 5838</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>762; 6771</t>
+          <t>628; 6640</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1996; 9745</t>
+          <t>2005; 9974</t>
         </is>
       </c>
     </row>
@@ -2185,32 +2185,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2238,32 +2238,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2588</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>850</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>873</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>1620</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>2581</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2588</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>850</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4884</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 5757</t>
+          <t>642; 6012</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>659; 7091</t>
+          <t>0; 5057</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4361</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>663; 6027</t>
+          <t>0; 6070</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 4266</t>
+          <t>656; 6346</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 3916</t>
+          <t>0; 4358</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1923; 9095</t>
+          <t>1592; 8493</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>858; 7333</t>
+          <t>1293; 8281</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>644</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3931</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 2958</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 3865</t>
+          <t>0; 3251</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2511,32 +2511,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2564,32 +2564,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>2837</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>6218</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>5388</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>2103</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>8630</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>8540</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>2837</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>6218</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>5388</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>599; 6316</t>
+          <t>692; 7329</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4492; 14748</t>
+          <t>2866; 11283</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4770; 14824</t>
+          <t>2453; 10666</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>683; 6765</t>
+          <t>596; 5673</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2827; 11033</t>
+          <t>4663; 15113</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2208; 10268</t>
+          <t>4598; 14913</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2101; 10089</t>
+          <t>1931; 9470</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>9206; 22381</t>
+          <t>9502; 22080</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>8463; 22061</t>
+          <t>8761; 20758</t>
         </is>
       </c>
     </row>
